--- a/data/trans_dic/P1001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,44</t>
+          <t>1,37; 4,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,44</t>
+          <t>1,0; 3,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,25</t>
+          <t>1,14; 4,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,28</t>
+          <t>0,83; 7,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,64</t>
+          <t>1,49; 4,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,72</t>
+          <t>2,82; 7,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,3</t>
+          <t>1,78; 5,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,41; 13,33</t>
+          <t>4,53; 14,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,76; 3,78</t>
+          <t>1,83; 4,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,55</t>
+          <t>2,29; 4,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,1</t>
+          <t>1,68; 3,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,19; 8,47</t>
+          <t>3,14; 8,34</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 4,81</t>
+          <t>2,2; 4,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,75</t>
+          <t>1,79; 4,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,47</t>
+          <t>2,87; 6,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,22</t>
+          <t>0,95; 5,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,4; 9,61</t>
+          <t>5,46; 9,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,77; 7,54</t>
+          <t>3,7; 7,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 6,62</t>
+          <t>3,2; 6,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,03; 8,7</t>
+          <t>3,22; 8,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,99; 6,63</t>
+          <t>3,9; 6,34</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,46</t>
+          <t>3,11; 5,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,48; 5,82</t>
+          <t>3,46; 5,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 6,16</t>
+          <t>2,77; 6,01</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,61; 5,96</t>
+          <t>2,78; 6,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,55</t>
+          <t>3,66; 7,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,22; 6,68</t>
+          <t>3,2; 6,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,84; 8,33</t>
+          <t>3,97; 8,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,97; 8,81</t>
+          <t>4,84; 8,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,44; 14,41</t>
+          <t>9,28; 14,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,97</t>
+          <t>5,05; 8,72</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 7,65</t>
+          <t>4,23; 7,54</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 6,88</t>
+          <t>4,38; 6,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,26</t>
+          <t>7,1; 10,24</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,51; 7,12</t>
+          <t>4,58; 7,2</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,47; 7,2</t>
+          <t>4,55; 7,3</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,26; 8,44</t>
+          <t>4,46; 9,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 9,57</t>
+          <t>4,89; 9,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,02; 9,21</t>
+          <t>4,97; 9,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,17; 7,65</t>
+          <t>2,03; 7,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 14,3</t>
+          <t>8,67; 14,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,99; 16,53</t>
+          <t>10,81; 16,6</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 13,09</t>
+          <t>8,35; 12,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,2; 11,78</t>
+          <t>7,21; 11,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 10,9</t>
+          <t>7,13; 10,7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 12,18</t>
+          <t>8,33; 11,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 10,35</t>
+          <t>7,19; 10,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 8,59</t>
+          <t>4,13; 8,65</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,84; 11,22</t>
+          <t>5,78; 11,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 13,04</t>
+          <t>6,99; 12,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 9,69</t>
+          <t>4,78; 9,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 10,02</t>
+          <t>5,79; 9,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,4</t>
+          <t>8,15; 14,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,15; 24,78</t>
+          <t>16,78; 24,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,46; 21,82</t>
+          <t>14,42; 21,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,12; 15,53</t>
+          <t>11,22; 15,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,8; 12,18</t>
+          <t>7,69; 11,91</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>12,73; 17,85</t>
+          <t>13,03; 17,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,28; 15,0</t>
+          <t>10,38; 14,93</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,88; 12,03</t>
+          <t>8,89; 12,05</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,39; 15,8</t>
+          <t>8,78; 16,02</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,63; 16,2</t>
+          <t>8,76; 16,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,68; 12,24</t>
+          <t>5,89; 12,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 9,87</t>
+          <t>5,78; 10,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 18,12</t>
+          <t>10,98; 17,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,14; 27,99</t>
+          <t>19,06; 27,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18,16; 26,23</t>
+          <t>17,83; 26,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,06; 15,78</t>
+          <t>4,27; 15,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,47; 15,95</t>
+          <t>10,73; 16,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,9; 21,04</t>
+          <t>14,66; 21,04</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,73; 18,43</t>
+          <t>13,23; 18,7</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,37; 12,2</t>
+          <t>4,25; 12,08</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,1; 22,36</t>
+          <t>12,18; 22,17</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>16,84; 28,5</t>
+          <t>17,3; 27,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8,93; 17,13</t>
+          <t>9,43; 17,22</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,91; 15,24</t>
+          <t>8,94; 14,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,46; 23,77</t>
+          <t>14,7; 23,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,28; 38,4</t>
+          <t>28,42; 38,31</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,32; 32,7</t>
+          <t>23,1; 33,16</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,05; 29,3</t>
+          <t>23,11; 29,73</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,66; 21,49</t>
+          <t>14,69; 21,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,21; 32,63</t>
+          <t>25,51; 32,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,21; 25,72</t>
+          <t>18,29; 25,53</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,11; 22,59</t>
+          <t>18,09; 22,59</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,87</t>
+          <t>5,25; 6,98</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,09</t>
+          <t>6,18; 8,02</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,34; 6,96</t>
+          <t>5,3; 6,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,43; 6,68</t>
+          <t>4,36; 6,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,38; 10,5</t>
+          <t>8,45; 10,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,51; 15,92</t>
+          <t>13,52; 15,99</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,11; 13,29</t>
+          <t>11,03; 13,42</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,89; 11,93</t>
+          <t>8,83; 12,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,1; 8,42</t>
+          <t>7,14; 8,38</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,17; 11,69</t>
+          <t>10,18; 11,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,53; 9,89</t>
+          <t>8,58; 9,9</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,25; 9,2</t>
+          <t>7,22; 9,17</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales</t>
+          <t>Población que hizo menos de lo que hubiera querido por problemas emocionales (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>7039; 21952</t>
+          <t>6761; 21673</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4518; 15613</t>
+          <t>4559; 16560</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4347; 17818</t>
+          <t>4761; 18264</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3315; 33127</t>
+          <t>3329; 28679</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7153; 21706</t>
+          <t>6969; 20870</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11506; 28895</t>
+          <t>12121; 31444</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6849; 20991</t>
+          <t>7052; 21209</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>13820; 41748</t>
+          <t>14197; 44182</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>16910; 36355</t>
+          <t>17589; 38606</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>19495; 40230</t>
+          <t>20274; 41430</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13492; 33419</t>
+          <t>13712; 32075</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22745; 60396</t>
+          <t>22403; 59480</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15969; 35406</t>
+          <t>16170; 35958</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12403; 32630</t>
+          <t>12323; 33375</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16589; 38216</t>
+          <t>16921; 39219</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3961; 22097</t>
+          <t>4036; 23592</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33758; 60091</t>
+          <t>34127; 61017</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23016; 46033</t>
+          <t>22562; 47162</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>17832; 37288</t>
+          <t>18039; 37119</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15508; 44482</t>
+          <t>16475; 44230</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>54290; 90248</t>
+          <t>53046; 86314</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41361; 70790</t>
+          <t>40411; 70394</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40173; 67121</t>
+          <t>39947; 69014</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25610; 57609</t>
+          <t>25897; 56187</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16671; 38051</t>
+          <t>17737; 39057</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>26291; 51444</t>
+          <t>24923; 50656</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21568; 44677</t>
+          <t>21442; 43422</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20590; 44684</t>
+          <t>21302; 44424</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34314; 60768</t>
+          <t>33392; 60124</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67075; 102414</t>
+          <t>65980; 102005</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33350; 59332</t>
+          <t>33422; 57646</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>23833; 41506</t>
+          <t>22972; 40882</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56475; 91362</t>
+          <t>58192; 90560</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>100406; 142794</t>
+          <t>98883; 142534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>59947; 94747</t>
+          <t>60887; 95784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>48170; 77694</t>
+          <t>49104; 78789</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>22114; 43799</t>
+          <t>23150; 46726</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>30119; 58700</t>
+          <t>29981; 58225</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32415; 59514</t>
+          <t>32091; 59889</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>19223; 67935</t>
+          <t>17989; 67003</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44454; 73732</t>
+          <t>44692; 73743</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>67741; 101845</t>
+          <t>66609; 102314</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52665; 84985</t>
+          <t>54171; 84341</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51271; 83899</t>
+          <t>51330; 82637</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74574; 112766</t>
+          <t>73785; 110743</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>103934; 149808</t>
+          <t>102452; 147456</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91354; 134058</t>
+          <t>93069; 134127</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66797; 137515</t>
+          <t>66018; 138465</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22589; 43404</t>
+          <t>22338; 44035</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30653; 55989</t>
+          <t>30024; 53839</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22897; 46304</t>
+          <t>22833; 45427</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33180; 56221</t>
+          <t>32468; 55614</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>33351; 58180</t>
+          <t>32908; 58035</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>76633; 110683</t>
+          <t>74986; 108013</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71849; 108402</t>
+          <t>71633; 106826</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>60892; 85064</t>
+          <t>61422; 85017</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>61670; 96281</t>
+          <t>60771; 94204</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>111574; 156356</t>
+          <t>114152; 155706</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>100210; 146220</t>
+          <t>101181; 145543</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>98413; 133431</t>
+          <t>98629; 133627</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>24550; 46234</t>
+          <t>25676; 46858</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>26750; 50193</t>
+          <t>27129; 52583</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18997; 40925</t>
+          <t>19691; 41125</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>20195; 36273</t>
+          <t>21264; 37628</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37739; 62129</t>
+          <t>37665; 61679</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67561; 98806</t>
+          <t>67282; 97842</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>68616; 99091</t>
+          <t>67357; 99285</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>24700; 96021</t>
+          <t>25948; 96816</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66525; 101360</t>
+          <t>68205; 103688</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>98737; 139492</t>
+          <t>97194; 139429</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>90630; 131211</t>
+          <t>94185; 133193</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>42627; 119039</t>
+          <t>41441; 117848</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25397; 46928</t>
+          <t>25563; 46534</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>42084; 71206</t>
+          <t>43217; 69736</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22940; 44016</t>
+          <t>24225; 44247</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25150; 42987</t>
+          <t>25211; 42281</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48281; 79370</t>
+          <t>49089; 79976</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>109995; 149368</t>
+          <t>110561; 149019</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>89332; 130853</t>
+          <t>92442; 132686</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>97817; 124358</t>
+          <t>98074; 126183</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79726; 116850</t>
+          <t>79860; 116813</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>161021; 208474</t>
+          <t>162978; 210383</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>119658; 169028</t>
+          <t>120220; 167775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>127960; 159591</t>
+          <t>127814; 159600</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>172453; 225005</t>
+          <t>171962; 228714</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>213601; 277081</t>
+          <t>211723; 274717</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>181184; 236112</t>
+          <t>179888; 236610</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>153091; 230943</t>
+          <t>150804; 230107</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>283244; 354868</t>
+          <t>285475; 353205</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>480563; 566098</t>
+          <t>480889; 568669</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>393719; 471155</t>
+          <t>390919; 475836</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>325389; 436584</t>
+          <t>323034; 440327</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>472859; 560462</t>
+          <t>475327; 557935</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>709853; 815980</t>
+          <t>710869; 817586</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>592027; 686199</t>
+          <t>595029; 687165</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>516011; 654703</t>
+          <t>514146; 652784</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1001-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P1001-Edad-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,39</t>
+          <t>1,31; 4,41</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,65</t>
+          <t>1,02; 3,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 4,35</t>
+          <t>1,01; 4,19</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 7,17</t>
+          <t>0,8; 6,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 4,46</t>
+          <t>1,37; 4,53</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 7,31</t>
+          <t>2,89; 6,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,78; 5,36</t>
+          <t>1,63; 5,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,53; 14,11</t>
+          <t>4,55; 13,17</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,02</t>
+          <t>1,73; 4,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,68</t>
+          <t>2,15; 4,59</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,68; 3,93</t>
+          <t>1,73; 4,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,14; 8,34</t>
+          <t>3,29; 8,46</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,89</t>
+          <t>2,21; 4,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,79; 4,86</t>
+          <t>1,82; 4,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,87; 6,64</t>
+          <t>3,05; 6,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,57</t>
+          <t>0,88; 5,07</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,46; 9,76</t>
+          <t>5,45; 9,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,73</t>
+          <t>3,83; 7,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,59</t>
+          <t>3,21; 6,65</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 8,65</t>
+          <t>4,22; 9,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,9; 6,34</t>
+          <t>3,93; 6,48</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 5,43</t>
+          <t>3,1; 5,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,98</t>
+          <t>3,36; 5,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,77; 6,01</t>
+          <t>2,99; 6,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,67%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,12</t>
+          <t>2,79; 6,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,66; 7,44</t>
+          <t>3,91; 7,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 6,49</t>
+          <t>3,25; 6,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,97; 8,28</t>
+          <t>3,62; 7,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 8,72</t>
+          <t>4,99; 8,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,28; 14,35</t>
+          <t>9,09; 14,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,05; 8,72</t>
+          <t>5,01; 8,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4,23; 7,54</t>
+          <t>4,6; 7,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,82</t>
+          <t>4,19; 6,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,1; 10,24</t>
+          <t>7,08; 10,23</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,2</t>
+          <t>4,54; 7,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,3</t>
+          <t>4,59; 7,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4,46; 9,0</t>
+          <t>4,36; 8,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,49</t>
+          <t>4,91; 9,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,97; 9,27</t>
+          <t>5,12; 9,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,55</t>
+          <t>4,78; 8,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,67; 14,3</t>
+          <t>8,75; 14,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,81; 16,6</t>
+          <t>10,62; 16,47</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 12,99</t>
+          <t>8,15; 13,42</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,6</t>
+          <t>7,25; 10,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,13; 10,7</t>
+          <t>7,15; 10,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,33; 11,99</t>
+          <t>8,56; 12,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 10,36</t>
+          <t>7,13; 10,68</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,65</t>
+          <t>6,51; 9,13</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,78; 11,39</t>
+          <t>5,79; 11,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,99; 12,54</t>
+          <t>7,21; 12,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,78; 9,51</t>
+          <t>4,69; 9,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,91</t>
+          <t>5,4; 9,35</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,15; 14,37</t>
+          <t>8,31; 14,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,78; 24,18</t>
+          <t>16,61; 24,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,42; 21,5</t>
+          <t>14,48; 21,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>11,22; 15,53</t>
+          <t>11,36; 15,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,91</t>
+          <t>7,78; 11,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,03; 17,77</t>
+          <t>13,06; 17,94</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10,38; 14,93</t>
+          <t>10,4; 14,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,05</t>
+          <t>8,92; 11,76</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8,78; 16,02</t>
+          <t>8,56; 16,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,76; 16,97</t>
+          <t>8,34; 16,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,89; 12,3</t>
+          <t>6,03; 12,36</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,78; 10,24</t>
+          <t>5,75; 10,22</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,98; 17,99</t>
+          <t>10,8; 17,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,06; 27,71</t>
+          <t>18,58; 27,22</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,83; 26,28</t>
+          <t>17,58; 26,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4,27; 15,91</t>
+          <t>13,13; 18,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,32</t>
+          <t>10,77; 15,84</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14,66; 21,04</t>
+          <t>14,91; 21,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>13,23; 18,7</t>
+          <t>13,0; 18,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 12,08</t>
+          <t>10,11; 13,72</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>12,18; 22,17</t>
+          <t>12,32; 22,24</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17,3; 27,91</t>
+          <t>16,96; 28,36</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,43; 17,22</t>
+          <t>9,02; 16,97</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8,94; 14,99</t>
+          <t>9,1; 15,09</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,7; 23,95</t>
+          <t>14,31; 23,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,42; 38,31</t>
+          <t>28,47; 38,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,1; 33,16</t>
+          <t>22,2; 32,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,11; 29,73</t>
+          <t>23,77; 29,84</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14,69; 21,48</t>
+          <t>15,12; 21,58</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25,51; 32,93</t>
+          <t>25,49; 33,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18,29; 25,53</t>
+          <t>18,39; 25,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,09; 22,59</t>
+          <t>18,49; 23,0</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,25; 6,98</t>
+          <t>5,25; 6,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,18; 8,02</t>
+          <t>6,28; 8,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5,3; 6,97</t>
+          <t>5,26; 6,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4,36; 6,65</t>
+          <t>5,25; 6,9</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>8,45; 10,45</t>
+          <t>8,41; 10,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,52; 15,99</t>
+          <t>13,61; 15,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,03; 13,42</t>
+          <t>10,96; 13,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,03</t>
+          <t>10,84; 12,65</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,14; 8,38</t>
+          <t>7,11; 8,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10,18; 11,71</t>
+          <t>10,2; 11,76</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8,58; 9,9</t>
+          <t>8,5; 9,9</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,22; 9,17</t>
+          <t>8,34; 9,62</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11489</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37394</t>
+          <t>40435</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6761; 21673</t>
+          <t>6465; 21789</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4559; 16560</t>
+          <t>4620; 15866</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4761; 18264</t>
+          <t>4218; 17590</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3329; 28679</t>
+          <t>3252; 28154</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6969; 20870</t>
+          <t>6427; 21178</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12121; 31444</t>
+          <t>12446; 30071</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7052; 21209</t>
+          <t>6462; 20907</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14197; 44182</t>
+          <t>16501; 47741</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17589; 38606</t>
+          <t>16617; 38629</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>20274; 41430</t>
+          <t>18993; 40569</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13712; 32075</t>
+          <t>14117; 33207</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22403; 59480</t>
+          <t>25332; 65149</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9920</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>28934</t>
+          <t>31339</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>43032</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>16170; 35958</t>
+          <t>16258; 34716</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12323; 33375</t>
+          <t>12500; 32233</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16921; 39219</t>
+          <t>18001; 38453</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4036; 23592</t>
+          <t>4215; 24174</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34127; 61017</t>
+          <t>34088; 60265</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22562; 47162</t>
+          <t>23362; 48068</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18039; 37119</t>
+          <t>18102; 37488</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16475; 44230</t>
+          <t>21169; 47232</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>53046; 86314</t>
+          <t>53450; 88182</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40411; 70394</t>
+          <t>40236; 71391</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39947; 69014</t>
+          <t>38833; 68984</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25897; 56187</t>
+          <t>29249; 59478</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>32668</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31477</t>
+          <t>37814</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62415</t>
+          <t>70481</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>17737; 39057</t>
+          <t>17797; 40446</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24923; 50656</t>
+          <t>26625; 51357</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>21442; 43422</t>
+          <t>21728; 44905</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21302; 44424</t>
+          <t>22455; 47578</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33392; 60124</t>
+          <t>34391; 60922</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>65980; 102005</t>
+          <t>64595; 100597</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>33422; 57646</t>
+          <t>33134; 59046</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>22972; 40882</t>
+          <t>28610; 48790</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58192; 90560</t>
+          <t>55710; 90541</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>98883; 142534</t>
+          <t>98483; 142357</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60887; 95784</t>
+          <t>60363; 94326</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>49104; 78789</t>
+          <t>57092; 86980</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43579</t>
+          <t>45195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>64362</t>
+          <t>65861</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>107940</t>
+          <t>111056</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>23150; 46726</t>
+          <t>22641; 44551</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29981; 58225</t>
+          <t>30146; 57664</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32091; 59889</t>
+          <t>33070; 61155</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17989; 67003</t>
+          <t>33511; 61661</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44692; 73743</t>
+          <t>45122; 74051</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66609; 102314</t>
+          <t>65462; 101464</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54171; 84341</t>
+          <t>52921; 87134</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>51330; 82637</t>
+          <t>53362; 78397</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>73785; 110743</t>
+          <t>73941; 109632</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>102452; 147456</t>
+          <t>105329; 150794</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93069; 134127</t>
+          <t>92314; 138257</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>66018; 138465</t>
+          <t>93540; 131180</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42209</t>
+          <t>43657</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>72338</t>
+          <t>82038</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>114547</t>
+          <t>125695</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>22338; 44035</t>
+          <t>22384; 43050</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>30024; 53839</t>
+          <t>30975; 55206</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22833; 45427</t>
+          <t>22422; 44011</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>32468; 55614</t>
+          <t>32886; 56973</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32908; 58035</t>
+          <t>33576; 58109</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>74986; 108013</t>
+          <t>74207; 111651</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>71633; 106826</t>
+          <t>71943; 108348</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>61422; 85017</t>
+          <t>69103; 96593</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60771; 94204</t>
+          <t>61532; 93311</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>114152; 155706</t>
+          <t>114471; 157213</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>101181; 145543</t>
+          <t>101375; 142051</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>98629; 133627</t>
+          <t>108677; 143237</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28507</t>
+          <t>31152</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>60899</t>
+          <t>68749</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>89405</t>
+          <t>99901</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>25676; 46858</t>
+          <t>25052; 47368</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>27129; 52583</t>
+          <t>25838; 50467</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19691; 41125</t>
+          <t>20162; 41326</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21264; 37628</t>
+          <t>23364; 41546</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>37665; 61679</t>
+          <t>37041; 61662</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>67282; 97842</t>
+          <t>65601; 96107</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>67357; 99285</t>
+          <t>66418; 100215</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25948; 96816</t>
+          <t>57657; 80720</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>68205; 103688</t>
+          <t>68446; 100644</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>97194; 139429</t>
+          <t>98857; 139996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>94185; 133193</t>
+          <t>92543; 132574</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>41441; 117848</t>
+          <t>85479; 116017</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32563</t>
+          <t>37255</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>110872</t>
+          <t>123261</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>143435</t>
+          <t>160516</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25563; 46534</t>
+          <t>25863; 46683</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43217; 69736</t>
+          <t>42367; 70860</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24225; 44247</t>
+          <t>23189; 43614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25211; 42281</t>
+          <t>28172; 46731</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>49089; 79976</t>
+          <t>47795; 77958</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>110561; 149019</t>
+          <t>110751; 150437</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>92442; 132686</t>
+          <t>88854; 130283</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>98074; 126183</t>
+          <t>110093; 138227</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79860; 116813</t>
+          <t>82197; 117331</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162978; 210383</t>
+          <t>162853; 211469</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>120220; 167775</t>
+          <t>120878; 166599</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>127814; 159600</t>
+          <t>142890; 177764</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>198990</t>
+          <t>213109</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>395001</t>
+          <t>438009</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>593991</t>
+          <t>651118</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>171962; 228714</t>
+          <t>171921; 227118</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>211723; 274717</t>
+          <t>214993; 280066</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>179888; 236610</t>
+          <t>178431; 235824</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>150804; 230107</t>
+          <t>185392; 243544</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>285475; 353205</t>
+          <t>284255; 353412</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>480889; 568669</t>
+          <t>483844; 565020</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>390919; 475836</t>
+          <t>388455; 477619</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>323034; 440327</t>
+          <t>404522; 472033</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>475327; 557935</t>
+          <t>473518; 564186</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>710869; 817586</t>
+          <t>711750; 820954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>595029; 687165</t>
+          <t>589503; 686955</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>514146; 652784</t>
+          <t>605652; 698833</t>
         </is>
       </c>
     </row>
